--- a/Export_Vorlage/Haltungen.xlsx
+++ b/Export_Vorlage/Haltungen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haltungen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haltungen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Haltungen'!$A$26:$AA$5000</definedName>
@@ -817,13 +817,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -843,10 +843,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -863,10 +863,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF6600"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -883,10 +883,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -903,10 +903,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="AEB135"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -923,10 +923,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -942,8 +942,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -992,10 +992,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1004,13 +1004,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1030,10 +1030,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1050,10 +1050,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="E7E6E6"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1069,8 +1069,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1119,10 +1119,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1131,13 +1131,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1157,10 +1157,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1177,10 +1177,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1197,10 +1197,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF8000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1217,10 +1217,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1237,10 +1237,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1256,8 +1256,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1306,10 +1306,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1318,13 +1318,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1344,10 +1344,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1364,10 +1364,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="BF8F00"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1384,10 +1384,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1404,10 +1404,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1424,10 +1424,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1443,8 +1443,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1493,10 +1493,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1505,13 +1505,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1531,10 +1531,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1551,10 +1551,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00B050"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1571,10 +1571,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1590,8 +1590,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1640,10 +1640,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1678,17 +1678,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6A6A6"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1696,10 +1696,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="3F3F46"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1707,10 +1707,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="808080"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1718,10 +1718,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="FF6600"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1729,10 +1729,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="70AD47"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1740,10 +1740,10 @@
           <dPt>
             <idx val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D6DCE4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1762,8 +1762,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1794,8 +1794,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1824,10 +1824,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1836,13 +1836,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1862,17 +1862,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="548235"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1880,10 +1880,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="FFFF00"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1891,10 +1891,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="FF8000"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1902,10 +1902,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="00B0F0"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1913,10 +1913,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1935,8 +1935,8 @@
         <dLbls>
           <numFmt formatCode="#,##0 &quot;CHF&quot;;;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1967,8 +1967,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1997,10 +1997,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2009,7 +2009,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="3024000" y="72000"/>
     <ext cx="4680000" cy="558000"/>
@@ -2019,9 +2019,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2036,9 +2036,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2053,9 +2053,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2070,9 +2070,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2087,9 +2087,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2104,9 +2104,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2121,9 +2121,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2138,13 +2138,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2622,11 +2622,11 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>AWU</t>
+          <t>Abwasser Uri</t>
         </is>
       </c>
       <c r="E17" s="12">
-        <f>COUNTIF($O$27:$O$5000,"AWU")</f>
+        <f>COUNTIF($O$27:$O$5000,"Abwasser Uri")+COUNTIF($O$27:$O$5000,"AWU")</f>
         <v/>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -2668,13 +2668,13 @@
       </c>
       <c r="O17" s="16" t="inlineStr">
         <is>
-          <t>Total AWU</t>
+          <t>Total Abwasser Uri</t>
         </is>
       </c>
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="17">
-        <f>SUMIF($O$27:$O$5000,"AWU",$N$27:$N$5000)</f>
+        <f>SUMIF($O$27:$O$5000,"Abwasser Uri",$N$27:$N$5000)+SUMIF($O$27:$O$5000,"AWU",$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S17" s="16" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Kanton</t>
+          <t>Kanton Uri</t>
         </is>
       </c>
       <c r="E18" s="12">
-        <f>COUNTIF($O$27:$O$5000,"Kanton")</f>
+        <f>COUNTIF($O$27:$O$5000,"Kanton Uri")+COUNTIF($O$27:$O$5000,"Kanton")</f>
         <v/>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -2760,13 +2760,13 @@
       </c>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>Total Kanton</t>
+          <t>Total Kanton Uri</t>
         </is>
       </c>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="17">
-        <f>SUMIF($O$27:$O$5000,"Kanton",$N$27:$N$5000)</f>
+        <f>SUMIF($O$27:$O$5000,"Kanton Uri",$N$27:$N$5000)+SUMIF($O$27:$O$5000,"Kanton",$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S18" s="16" t="inlineStr">
@@ -3505,31 +3505,37 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="O27:O5000">
     <cfRule type="expression" priority="26" dxfId="0" stopIfTrue="1">
+      <formula>$O27="Abwasser Uri"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" dxfId="0" stopIfTrue="1">
       <formula>$O27="AWU"</formula>
     </cfRule>
-    <cfRule type="expression" priority="27" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="28" dxfId="6" stopIfTrue="1">
+      <formula>$O27="Kanton Uri"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" dxfId="6" stopIfTrue="1">
       <formula>$O27="Kanton"</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="30" dxfId="10" stopIfTrue="1">
       <formula>$O27="Bund"</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="31" dxfId="2" stopIfTrue="1">
       <formula>$O27="Gemeinde"</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="32" dxfId="4" stopIfTrue="1">
       <formula>$O27="Privat"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z27:Z5000">
-    <cfRule type="expression" priority="31" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="33" dxfId="4" stopIfTrue="1">
       <formula>$Z27="offen"</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" dxfId="11" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="11" stopIfTrue="1">
       <formula>$Z27="abgeschlossen"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:AA5000">
-    <cfRule type="expression" priority="33" dxfId="12">
+    <cfRule type="expression" priority="35" dxfId="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
